--- a/project1/Z_Documentation/Project1_Tracker.xlsx
+++ b/project1/Z_Documentation/Project1_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://waynestateprod-my.sharepoint.com/personal/gw3477_wayne_edu/Documents/DSE 6100/Project 1/database_javascript/project1/Z_Documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C93CC18F-2536-465B-BF22-C77A98FAF5EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{C93CC18F-2536-465B-BF22-C77A98FAF5EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{11431AC6-99C1-4962-A2DF-CE1B014ADE13}"/>
   <bookViews>
-    <workbookView xWindow="-93" yWindow="-93" windowWidth="25786" windowHeight="15466" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-93" yWindow="-93" windowWidth="25786" windowHeight="15466" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="File map" sheetId="1" r:id="rId1"/>
@@ -1462,6 +1462,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85571BBE-1456-4B5D-BA86-ED464C6FFE36}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:G52"/>
   <sheetFormatPr defaultColWidth="8.703125" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
@@ -1552,7 +1553,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="25.35" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:7" ht="25.35" hidden="1" x14ac:dyDescent="0.5">
       <c r="A9" s="19">
         <v>1</v>
       </c>
@@ -1571,7 +1572,7 @@
       <c r="F9" s="16"/>
       <c r="G9" s="16"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.5">
       <c r="A10" s="19">
         <v>2</v>
       </c>
@@ -1590,7 +1591,7 @@
       <c r="F10" s="16"/>
       <c r="G10" s="16"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.5">
       <c r="A11" s="19">
         <v>3</v>
       </c>
@@ -1609,7 +1610,7 @@
       <c r="F11" s="16"/>
       <c r="G11" s="16"/>
     </row>
-    <row r="12" spans="1:7" ht="25.35" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:7" ht="25.35" hidden="1" x14ac:dyDescent="0.5">
       <c r="A12" s="19">
         <v>4</v>
       </c>
@@ -1628,7 +1629,7 @@
       <c r="F12" s="16"/>
       <c r="G12" s="16"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.5">
       <c r="A13" s="19">
         <v>5</v>
       </c>
@@ -1647,7 +1648,7 @@
       <c r="F13" s="16"/>
       <c r="G13" s="16"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.5">
       <c r="A14" s="19">
         <v>6</v>
       </c>
@@ -1666,7 +1667,7 @@
       <c r="F14" s="16"/>
       <c r="G14" s="16"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.5">
       <c r="A15" s="19">
         <v>7</v>
       </c>
@@ -1685,7 +1686,7 @@
       <c r="F15" s="16"/>
       <c r="G15" s="16"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.5">
       <c r="A16" s="19">
         <v>8</v>
       </c>
@@ -1704,7 +1705,7 @@
       <c r="F16" s="16"/>
       <c r="G16" s="16"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.5">
       <c r="A17" s="19">
         <v>9</v>
       </c>
@@ -1723,7 +1724,7 @@
       <c r="F17" s="16"/>
       <c r="G17" s="16"/>
     </row>
-    <row r="18" spans="1:7" ht="25.35" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:7" ht="25.35" hidden="1" x14ac:dyDescent="0.5">
       <c r="A18" s="19">
         <v>10</v>
       </c>
@@ -1742,7 +1743,7 @@
       <c r="F18" s="16"/>
       <c r="G18" s="16"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.5">
       <c r="A19" s="19">
         <v>11</v>
       </c>
@@ -1761,7 +1762,7 @@
       <c r="F19" s="16"/>
       <c r="G19" s="16"/>
     </row>
-    <row r="20" spans="1:7" ht="25.35" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:7" ht="25.35" hidden="1" x14ac:dyDescent="0.5">
       <c r="A20" s="19">
         <v>12</v>
       </c>
@@ -1780,7 +1781,7 @@
       <c r="F20" s="16"/>
       <c r="G20" s="16"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:7" hidden="1" x14ac:dyDescent="0.5">
       <c r="A21" s="19">
         <v>13</v>
       </c>
@@ -1799,7 +1800,7 @@
       <c r="F21" s="16"/>
       <c r="G21" s="16"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.5">
       <c r="A22" s="19">
         <v>14</v>
       </c>
@@ -1818,7 +1819,7 @@
       <c r="F22" s="16"/>
       <c r="G22" s="16"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.5">
       <c r="A23" s="19">
         <v>15</v>
       </c>
@@ -1837,7 +1838,7 @@
       <c r="F23" s="16"/>
       <c r="G23" s="16"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.5">
       <c r="A24" s="19">
         <v>16</v>
       </c>
@@ -1913,7 +1914,7 @@
       <c r="F27" s="16"/>
       <c r="G27" s="16"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.5">
       <c r="A28" s="19">
         <v>20</v>
       </c>
@@ -1932,7 +1933,7 @@
       <c r="F28" s="16"/>
       <c r="G28" s="16"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.5">
       <c r="A29" s="19">
         <v>21</v>
       </c>
@@ -1951,7 +1952,7 @@
       <c r="F29" s="16"/>
       <c r="G29" s="16"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.5">
       <c r="A30" s="19">
         <v>22</v>
       </c>
@@ -1970,7 +1971,7 @@
       <c r="F30" s="16"/>
       <c r="G30" s="16"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.5">
       <c r="A31" s="19">
         <v>23</v>
       </c>
@@ -1989,7 +1990,7 @@
       <c r="F31" s="16"/>
       <c r="G31" s="16"/>
     </row>
-    <row r="32" spans="1:7" ht="25.35" x14ac:dyDescent="0.5">
+    <row r="32" spans="1:7" ht="25.35" hidden="1" x14ac:dyDescent="0.5">
       <c r="A32" s="19">
         <v>24</v>
       </c>
@@ -2008,7 +2009,7 @@
       <c r="F32" s="16"/>
       <c r="G32" s="16"/>
     </row>
-    <row r="33" spans="1:7" ht="25.35" x14ac:dyDescent="0.5">
+    <row r="33" spans="1:7" ht="25.35" hidden="1" x14ac:dyDescent="0.5">
       <c r="A33" s="19">
         <v>25</v>
       </c>
@@ -2027,7 +2028,7 @@
       <c r="F33" s="16"/>
       <c r="G33" s="16"/>
     </row>
-    <row r="34" spans="1:7" ht="25.35" x14ac:dyDescent="0.5">
+    <row r="34" spans="1:7" ht="25.35" hidden="1" x14ac:dyDescent="0.5">
       <c r="A34" s="19">
         <v>26</v>
       </c>
@@ -2046,7 +2047,7 @@
       <c r="F34" s="16"/>
       <c r="G34" s="16"/>
     </row>
-    <row r="35" spans="1:7" ht="25.35" x14ac:dyDescent="0.5">
+    <row r="35" spans="1:7" ht="25.35" hidden="1" x14ac:dyDescent="0.5">
       <c r="A35" s="19">
         <v>27</v>
       </c>
@@ -2065,7 +2066,7 @@
       <c r="F35" s="16"/>
       <c r="G35" s="16"/>
     </row>
-    <row r="36" spans="1:7" ht="25.35" x14ac:dyDescent="0.5">
+    <row r="36" spans="1:7" ht="25.35" hidden="1" x14ac:dyDescent="0.5">
       <c r="A36" s="19">
         <v>28</v>
       </c>
@@ -2084,7 +2085,7 @@
       <c r="F36" s="16"/>
       <c r="G36" s="16"/>
     </row>
-    <row r="37" spans="1:7" ht="25.35" x14ac:dyDescent="0.5">
+    <row r="37" spans="1:7" ht="25.35" hidden="1" x14ac:dyDescent="0.5">
       <c r="A37" s="19">
         <v>29</v>
       </c>
@@ -2103,7 +2104,7 @@
       <c r="F37" s="16"/>
       <c r="G37" s="16"/>
     </row>
-    <row r="38" spans="1:7" ht="25.35" x14ac:dyDescent="0.5">
+    <row r="38" spans="1:7" ht="25.35" hidden="1" x14ac:dyDescent="0.5">
       <c r="A38" s="19">
         <v>30</v>
       </c>
@@ -2122,7 +2123,7 @@
       <c r="F38" s="16"/>
       <c r="G38" s="16"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.5">
       <c r="A39" s="19">
         <v>31</v>
       </c>
@@ -2141,7 +2142,7 @@
       <c r="F39" s="16"/>
       <c r="G39" s="16"/>
     </row>
-    <row r="40" spans="1:7" ht="25.35" x14ac:dyDescent="0.5">
+    <row r="40" spans="1:7" ht="25.35" hidden="1" x14ac:dyDescent="0.5">
       <c r="A40" s="19">
         <v>32</v>
       </c>
@@ -2160,7 +2161,7 @@
       <c r="F40" s="16"/>
       <c r="G40" s="16"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.5">
       <c r="A41" s="19">
         <v>33</v>
       </c>
@@ -2179,7 +2180,7 @@
       <c r="F41" s="16"/>
       <c r="G41" s="16"/>
     </row>
-    <row r="42" spans="1:7" ht="25.35" x14ac:dyDescent="0.5">
+    <row r="42" spans="1:7" ht="25.35" hidden="1" x14ac:dyDescent="0.5">
       <c r="A42" s="19">
         <v>34</v>
       </c>
@@ -2198,7 +2199,7 @@
       <c r="F42" s="16"/>
       <c r="G42" s="16"/>
     </row>
-    <row r="43" spans="1:7" ht="25.35" x14ac:dyDescent="0.5">
+    <row r="43" spans="1:7" ht="25.35" hidden="1" x14ac:dyDescent="0.5">
       <c r="A43" s="19">
         <v>35</v>
       </c>
@@ -2217,7 +2218,7 @@
       <c r="F43" s="16"/>
       <c r="G43" s="16"/>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.5">
       <c r="A44" s="19">
         <v>36</v>
       </c>
@@ -2236,7 +2237,7 @@
       <c r="F44" s="16"/>
       <c r="G44" s="16"/>
     </row>
-    <row r="45" spans="1:7" ht="25.35" x14ac:dyDescent="0.5">
+    <row r="45" spans="1:7" ht="25.35" hidden="1" x14ac:dyDescent="0.5">
       <c r="A45" s="19">
         <v>37</v>
       </c>
@@ -2255,7 +2256,7 @@
       <c r="F45" s="16"/>
       <c r="G45" s="16"/>
     </row>
-    <row r="46" spans="1:7" ht="25.35" x14ac:dyDescent="0.5">
+    <row r="46" spans="1:7" ht="25.35" hidden="1" x14ac:dyDescent="0.5">
       <c r="A46" s="19">
         <v>38</v>
       </c>
@@ -2274,7 +2275,7 @@
       <c r="F46" s="16"/>
       <c r="G46" s="16"/>
     </row>
-    <row r="47" spans="1:7" ht="25.35" x14ac:dyDescent="0.5">
+    <row r="47" spans="1:7" ht="25.35" hidden="1" x14ac:dyDescent="0.5">
       <c r="A47" s="19">
         <v>39</v>
       </c>
@@ -2293,7 +2294,7 @@
       <c r="F47" s="16"/>
       <c r="G47" s="16"/>
     </row>
-    <row r="48" spans="1:7" ht="25.35" x14ac:dyDescent="0.5">
+    <row r="48" spans="1:7" ht="25.35" hidden="1" x14ac:dyDescent="0.5">
       <c r="A48" s="19">
         <v>40</v>
       </c>
@@ -2312,7 +2313,7 @@
       <c r="F48" s="16"/>
       <c r="G48" s="16"/>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.5">
       <c r="A49" s="19">
         <v>41</v>
       </c>
@@ -2331,7 +2332,7 @@
       <c r="F49" s="16"/>
       <c r="G49" s="16"/>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.5">
       <c r="A50" s="19">
         <v>42</v>
       </c>
@@ -2350,7 +2351,7 @@
       <c r="F50" s="16"/>
       <c r="G50" s="16"/>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.5">
       <c r="A51" s="19">
         <v>43</v>
       </c>
@@ -2369,7 +2370,7 @@
       <c r="F51" s="16"/>
       <c r="G51" s="16"/>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.5">
       <c r="A52" s="19">
         <v>44</v>
       </c>
@@ -2389,7 +2390,13 @@
       <c r="G52" s="16"/>
     </row>
   </sheetData>
-  <autoFilter ref="A8:G52" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A8:G52" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="2. Database table and test data"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="1">
     <mergeCell ref="A2:G2"/>
   </mergeCells>
@@ -2566,4 +2573,10 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{e51cdec9-811d-471d-bbe6-dd3d8d54c28b}" enabled="0" method="" siteId="{e51cdec9-811d-471d-bbe6-dd3d8d54c28b}" removed="1"/>
+</clbl:labelList>
 </file>
--- a/project1/Z_Documentation/Project1_Tracker.xlsx
+++ b/project1/Z_Documentation/Project1_Tracker.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://waynestateprod-my.sharepoint.com/personal/gw3477_wayne_edu/Documents/DSE 6100/Project 1/database_javascript/project1/Z_Documentation/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Games\Tools and Utilities\XAMPP\htdocs\database_javascript\project1\Z_Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{C93CC18F-2536-465B-BF22-C77A98FAF5EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{11431AC6-99C1-4962-A2DF-CE1B014ADE13}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D74B42B2-57D5-4F7B-8640-2E05BD13A891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-93" yWindow="-93" windowWidth="25786" windowHeight="15466" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1185" yWindow="1815" windowWidth="21600" windowHeight="14130" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="File map" sheetId="1" r:id="rId1"/>
@@ -21,25 +21,12 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Checklist!$A$8:$G$52</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'File map'!$A$4:$E$15</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="199">
   <si>
     <t>DSE 6100 Project 1: main files</t>
   </si>
@@ -618,13 +605,31 @@
   </si>
   <si>
     <t>The 8 searches the panel needs</t>
+  </si>
+  <si>
+    <t>Not sure what this means, we do LIKE ? for a case insensitive search on username</t>
+  </si>
+  <si>
+    <t>Not sure what this is talking about; this is already the case</t>
+  </si>
+  <si>
+    <t>Not sure what this is talking about</t>
+  </si>
+  <si>
+    <t>Not sure what this means, we wouldn't use the registered date to find out users whom signed in today</t>
+  </si>
+  <si>
+    <t>Not necessary, we just edit after login</t>
+  </si>
+  <si>
+    <t>Necessary, we have to edit after login</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -713,6 +718,17 @@
       <name val="Arial"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -781,7 +797,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -815,12 +831,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -848,18 +858,30 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{FEA456FB-2D08-45A4-B267-54834F765DE8}"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="4">
     <dxf>
       <fill>
         <patternFill>
@@ -874,6 +896,20 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFE2EFDA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1176,28 +1212,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E21"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.234375" customWidth="1"/>
+    <col min="1" max="1" width="24.28515625" customWidth="1"/>
     <col min="2" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="80" customWidth="1"/>
     <col min="5" max="5" width="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="17.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A2" s="14" t="s">
+      <c r="B1" s="28"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -1214,7 +1250,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="25.35" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
@@ -1231,7 +1267,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="25.35" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
@@ -1248,7 +1284,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="25.35" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
@@ -1265,7 +1301,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="38" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
@@ -1282,7 +1318,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
@@ -1299,7 +1335,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="25.35" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>24</v>
       </c>
@@ -1316,7 +1352,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="50.7" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:5" ht="51" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>29</v>
       </c>
@@ -1333,7 +1369,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="38" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
         <v>29</v>
       </c>
@@ -1350,7 +1386,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="25.35" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>29</v>
       </c>
@@ -1367,7 +1403,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>29</v>
       </c>
@@ -1384,7 +1420,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="25.35" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
         <v>43</v>
       </c>
@@ -1401,12 +1437,12 @@
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="15.35" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B18" s="11" t="s">
         <v>49</v>
       </c>
@@ -1417,7 +1453,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B19" s="12" t="s">
         <v>51</v>
       </c>
@@ -1428,7 +1464,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="38" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:4" ht="38.25" x14ac:dyDescent="0.25">
       <c r="B20" s="12" t="s">
         <v>53</v>
       </c>
@@ -1439,7 +1475,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="50.7" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:4" ht="51" x14ac:dyDescent="0.25">
       <c r="B21" s="12" t="s">
         <v>56</v>
       </c>
@@ -1462,941 +1498,951 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85571BBE-1456-4B5D-BA86-ED464C6FFE36}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:G52"/>
-  <sheetFormatPr defaultColWidth="8.703125" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5" style="15" customWidth="1"/>
-    <col min="2" max="2" width="26" style="15" customWidth="1"/>
-    <col min="3" max="3" width="30" style="15" customWidth="1"/>
-    <col min="4" max="4" width="70" style="15" customWidth="1"/>
-    <col min="5" max="6" width="14" style="15" customWidth="1"/>
-    <col min="7" max="7" width="28" style="15" customWidth="1"/>
-    <col min="8" max="16384" width="8.703125" style="15"/>
+    <col min="1" max="1" width="5" style="13" customWidth="1"/>
+    <col min="2" max="2" width="26" style="13" customWidth="1"/>
+    <col min="3" max="3" width="30" style="13" customWidth="1"/>
+    <col min="4" max="4" width="70" style="13" customWidth="1"/>
+    <col min="5" max="6" width="14" style="13" customWidth="1"/>
+    <col min="7" max="7" width="28" style="13" customWidth="1"/>
+    <col min="8" max="16384" width="8.7109375" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="17.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="27" t="s">
+    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+      <c r="A1" s="24" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="26" t="s">
+    <row r="2" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="27" t="s">
         <v>167</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.5">
-      <c r="A4" s="25" t="s">
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="23" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.5">
-      <c r="B5" s="22" t="s">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="20" t="s">
         <v>165</v>
       </c>
-      <c r="C5" s="21">
+      <c r="C5" s="19">
         <f>COUNTA(C9:C52)</f>
         <v>44</v>
       </c>
-      <c r="D5" s="24" t="s">
+      <c r="D5" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="E5" s="23">
+      <c r="E5" s="21">
         <f>IFERROR(C6/C5,0)</f>
-        <v>2.2727272727272728E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.5">
-      <c r="B6" s="22" t="s">
+        <v>0.34090909090909088</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B6" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="C6" s="21">
+      <c r="C6" s="19">
         <f>COUNTIF(E9:E52,"Done")</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.5">
-      <c r="B7" s="22" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="20" t="s">
         <v>163</v>
       </c>
-      <c r="C7" s="21">
+      <c r="C7" s="19">
         <f>COUNTIF(E9:E52,"In progress")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.5">
-      <c r="A8" s="20" t="s">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="B8" s="20" t="s">
+      <c r="B8" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="C8" s="20" t="s">
+      <c r="C8" s="18" t="s">
         <v>160</v>
       </c>
-      <c r="D8" s="20" t="s">
+      <c r="D8" s="18" t="s">
         <v>159</v>
       </c>
-      <c r="E8" s="20" t="s">
+      <c r="E8" s="18" t="s">
         <v>158</v>
       </c>
-      <c r="F8" s="20" t="s">
+      <c r="F8" s="18" t="s">
         <v>157</v>
       </c>
-      <c r="G8" s="20" t="s">
+      <c r="G8" s="18" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="25.35" hidden="1" x14ac:dyDescent="0.5">
-      <c r="A9" s="19">
+    <row r="9" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="17">
         <v>1</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="16" t="s">
         <v>155</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="D9" s="14" t="s">
         <v>154</v>
       </c>
-      <c r="E9" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
-    </row>
-    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.5">
-      <c r="A10" s="19">
+      <c r="E9" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="17">
         <v>2</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="D10" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="E10" s="17" t="s">
+      <c r="E10" s="15" t="s">
         <v>151</v>
       </c>
-      <c r="F10" s="16"/>
-      <c r="G10" s="16"/>
-    </row>
-    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.5">
-      <c r="A11" s="19">
+      <c r="F10" s="14"/>
+      <c r="G10" s="14"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="17">
         <v>3</v>
       </c>
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="D11" s="16" t="s">
+      <c r="D11" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="E11" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
-    </row>
-    <row r="12" spans="1:7" ht="25.35" hidden="1" x14ac:dyDescent="0.5">
-      <c r="A12" s="19">
+      <c r="E11" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
+    </row>
+    <row r="12" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="17">
         <v>4</v>
       </c>
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="16" t="s">
         <v>148</v>
       </c>
-      <c r="D12" s="16" t="s">
+      <c r="D12" s="14" t="s">
         <v>147</v>
       </c>
-      <c r="E12" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
-    </row>
-    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.5">
-      <c r="A13" s="19">
+      <c r="E12" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="17">
         <v>5</v>
       </c>
-      <c r="B13" s="16" t="s">
+      <c r="B13" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="C13" s="18" t="s">
+      <c r="C13" s="16" t="s">
         <v>146</v>
       </c>
-      <c r="D13" s="16" t="s">
+      <c r="D13" s="14" t="s">
         <v>145</v>
       </c>
-      <c r="E13" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-    </row>
-    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.5">
-      <c r="A14" s="19">
+      <c r="E13" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="17">
         <v>6</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="C14" s="18" t="s">
+      <c r="C14" s="16" t="s">
         <v>144</v>
       </c>
-      <c r="D14" s="16" t="s">
+      <c r="D14" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="E14" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
-    </row>
-    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.5">
-      <c r="A15" s="19">
+      <c r="E14" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="17">
         <v>7</v>
       </c>
-      <c r="B15" s="16" t="s">
+      <c r="B15" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="C15" s="18" t="s">
+      <c r="C15" s="16" t="s">
         <v>142</v>
       </c>
-      <c r="D15" s="16" t="s">
+      <c r="D15" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="E15" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
-    </row>
-    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.5">
-      <c r="A16" s="19">
+      <c r="E15" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="17">
         <v>8</v>
       </c>
-      <c r="B16" s="16" t="s">
+      <c r="B16" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="C16" s="18" t="s">
+      <c r="C16" s="16" t="s">
         <v>140</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="D16" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="E16" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
-    </row>
-    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.5">
-      <c r="A17" s="19">
+      <c r="E16" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="F16" s="14"/>
+      <c r="G16" s="14"/>
+    </row>
+    <row r="17" spans="1:7" ht="51" x14ac:dyDescent="0.25">
+      <c r="A17" s="17">
         <v>9</v>
       </c>
-      <c r="B17" s="16" t="s">
+      <c r="B17" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="C17" s="18" t="s">
+      <c r="C17" s="16" t="s">
         <v>138</v>
       </c>
-      <c r="D17" s="16" t="s">
+      <c r="D17" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="E17" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="F17" s="16"/>
-      <c r="G17" s="16"/>
-    </row>
-    <row r="18" spans="1:7" ht="25.35" hidden="1" x14ac:dyDescent="0.5">
-      <c r="A18" s="19">
+      <c r="E17" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="F17" s="14"/>
+      <c r="G17" s="31" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="17">
         <v>10</v>
       </c>
-      <c r="B18" s="16" t="s">
+      <c r="B18" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="C18" s="18" t="s">
+      <c r="C18" s="16" t="s">
         <v>136</v>
       </c>
-      <c r="D18" s="16" t="s">
+      <c r="D18" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="E18" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="F18" s="16"/>
-      <c r="G18" s="16"/>
-    </row>
-    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.5">
-      <c r="A19" s="19">
+      <c r="E18" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="17">
         <v>11</v>
       </c>
-      <c r="B19" s="16" t="s">
+      <c r="B19" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="C19" s="18" t="s">
+      <c r="C19" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="D19" s="16" t="s">
+      <c r="D19" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="E19" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="F19" s="16"/>
-      <c r="G19" s="16"/>
-    </row>
-    <row r="20" spans="1:7" ht="25.35" hidden="1" x14ac:dyDescent="0.5">
-      <c r="A20" s="19">
+      <c r="E19" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="F19" s="14"/>
+      <c r="G19" s="14"/>
+    </row>
+    <row r="20" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A20" s="17">
         <v>12</v>
       </c>
-      <c r="B20" s="16" t="s">
+      <c r="B20" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="C20" s="18" t="s">
+      <c r="C20" s="16" t="s">
         <v>132</v>
       </c>
-      <c r="D20" s="16" t="s">
+      <c r="D20" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="E20" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="F20" s="16"/>
-      <c r="G20" s="16"/>
-    </row>
-    <row r="21" spans="1:7" hidden="1" x14ac:dyDescent="0.5">
-      <c r="A21" s="19">
+      <c r="E20" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="F20" s="14"/>
+      <c r="G20" s="14"/>
+    </row>
+    <row r="21" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A21" s="17">
         <v>13</v>
       </c>
-      <c r="B21" s="16" t="s">
+      <c r="B21" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="C21" s="18" t="s">
+      <c r="C21" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="D21" s="16" t="s">
+      <c r="D21" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="E21" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="F21" s="16"/>
-      <c r="G21" s="16"/>
-    </row>
-    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.5">
-      <c r="A22" s="19">
+      <c r="E21" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="F21" s="14"/>
+      <c r="G21" s="30" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A22" s="17">
         <v>14</v>
       </c>
-      <c r="B22" s="16" t="s">
+      <c r="B22" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="C22" s="18" t="s">
+      <c r="C22" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="D22" s="16" t="s">
+      <c r="D22" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="E22" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="F22" s="16"/>
-      <c r="G22" s="16"/>
-    </row>
-    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.5">
-      <c r="A23" s="19">
+      <c r="E22" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="F22" s="14"/>
+      <c r="G22" s="30" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A23" s="17">
         <v>15</v>
       </c>
-      <c r="B23" s="16" t="s">
+      <c r="B23" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="C23" s="18" t="s">
+      <c r="C23" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="D23" s="16" t="s">
+      <c r="D23" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="E23" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="F23" s="16"/>
-      <c r="G23" s="16"/>
-    </row>
-    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.5">
-      <c r="A24" s="19">
+      <c r="E23" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="F23" s="14"/>
+      <c r="G23" s="30" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="17">
         <v>16</v>
       </c>
-      <c r="B24" s="16" t="s">
+      <c r="B24" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="C24" s="18" t="s">
+      <c r="C24" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="D24" s="16" t="s">
+      <c r="D24" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="E24" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16"/>
-    </row>
-    <row r="25" spans="1:7" ht="25.35" x14ac:dyDescent="0.5">
-      <c r="A25" s="19">
+      <c r="E24" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+    </row>
+    <row r="25" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A25" s="17">
         <v>17</v>
       </c>
-      <c r="B25" s="16" t="s">
+      <c r="B25" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="C25" s="18" t="s">
+      <c r="C25" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="D25" s="16" t="s">
+      <c r="D25" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="E25" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="F25" s="16"/>
-      <c r="G25" s="16"/>
-    </row>
-    <row r="26" spans="1:7" ht="38" x14ac:dyDescent="0.5">
-      <c r="A26" s="19">
+      <c r="E25" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="F25" s="14"/>
+      <c r="G25" s="14"/>
+    </row>
+    <row r="26" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A26" s="17">
         <v>18</v>
       </c>
-      <c r="B26" s="16" t="s">
+      <c r="B26" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="C26" s="18" t="s">
+      <c r="C26" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="D26" s="16" t="s">
+      <c r="D26" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="E26" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="F26" s="16"/>
-      <c r="G26" s="16"/>
-    </row>
-    <row r="27" spans="1:7" ht="25.35" x14ac:dyDescent="0.5">
-      <c r="A27" s="19">
+      <c r="E26" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="F26" s="14"/>
+      <c r="G26" s="14"/>
+    </row>
+    <row r="27" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A27" s="17">
         <v>19</v>
       </c>
-      <c r="B27" s="16" t="s">
+      <c r="B27" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="C27" s="18" t="s">
+      <c r="C27" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="D27" s="16" t="s">
+      <c r="D27" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="E27" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="F27" s="16"/>
-      <c r="G27" s="16"/>
-    </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.5">
-      <c r="A28" s="19">
+      <c r="E27" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="F27" s="14"/>
+      <c r="G27" s="14"/>
+    </row>
+    <row r="28" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A28" s="17">
         <v>20</v>
       </c>
-      <c r="B28" s="16" t="s">
+      <c r="B28" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="C28" s="18" t="s">
+      <c r="C28" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="D28" s="16" t="s">
+      <c r="D28" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="E28" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="F28" s="16"/>
-      <c r="G28" s="16"/>
-    </row>
-    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.5">
-      <c r="A29" s="19">
+      <c r="E28" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="F28" s="14"/>
+      <c r="G28" s="14" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A29" s="17">
         <v>21</v>
       </c>
-      <c r="B29" s="16" t="s">
+      <c r="B29" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="C29" s="18" t="s">
+      <c r="C29" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="D29" s="16" t="s">
+      <c r="D29" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="E29" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="F29" s="16"/>
-      <c r="G29" s="16"/>
-    </row>
-    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.5">
-      <c r="A30" s="19">
+      <c r="E29" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="F29" s="14"/>
+      <c r="G29" s="14" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A30" s="17">
         <v>22</v>
       </c>
-      <c r="B30" s="16" t="s">
+      <c r="B30" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="C30" s="18" t="s">
+      <c r="C30" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="D30" s="16" t="s">
+      <c r="D30" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="E30" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="F30" s="16"/>
-      <c r="G30" s="16"/>
-    </row>
-    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.5">
-      <c r="A31" s="19">
+      <c r="E30" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A31" s="17">
         <v>23</v>
       </c>
-      <c r="B31" s="16" t="s">
+      <c r="B31" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="C31" s="18" t="s">
+      <c r="C31" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="D31" s="16" t="s">
+      <c r="D31" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="E31" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="F31" s="16"/>
-      <c r="G31" s="16"/>
-    </row>
-    <row r="32" spans="1:7" ht="25.35" hidden="1" x14ac:dyDescent="0.5">
-      <c r="A32" s="19">
+      <c r="E31" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="F31" s="14"/>
+      <c r="G31" s="14" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A32" s="17">
         <v>24</v>
       </c>
-      <c r="B32" s="16" t="s">
+      <c r="B32" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="C32" s="18" t="s">
+      <c r="C32" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="D32" s="16" t="s">
+      <c r="D32" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="E32" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="F32" s="16"/>
-      <c r="G32" s="16"/>
-    </row>
-    <row r="33" spans="1:7" ht="25.35" hidden="1" x14ac:dyDescent="0.5">
-      <c r="A33" s="19">
+      <c r="E32" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="F32" s="14"/>
+      <c r="G32" s="14" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A33" s="17">
         <v>25</v>
       </c>
-      <c r="B33" s="16" t="s">
+      <c r="B33" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="C33" s="18" t="s">
+      <c r="C33" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="D33" s="16" t="s">
+      <c r="D33" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="E33" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="F33" s="16"/>
-      <c r="G33" s="16"/>
-    </row>
-    <row r="34" spans="1:7" ht="25.35" hidden="1" x14ac:dyDescent="0.5">
-      <c r="A34" s="19">
+      <c r="E33" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="F33" s="14"/>
+      <c r="G33" s="14"/>
+    </row>
+    <row r="34" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A34" s="17">
         <v>26</v>
       </c>
-      <c r="B34" s="16" t="s">
+      <c r="B34" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="C34" s="18" t="s">
+      <c r="C34" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="D34" s="16" t="s">
+      <c r="D34" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="E34" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="F34" s="16"/>
-      <c r="G34" s="16"/>
-    </row>
-    <row r="35" spans="1:7" ht="25.35" hidden="1" x14ac:dyDescent="0.5">
-      <c r="A35" s="19">
+      <c r="E34" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="F34" s="14"/>
+      <c r="G34" s="14"/>
+    </row>
+    <row r="35" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A35" s="17">
         <v>27</v>
       </c>
-      <c r="B35" s="16" t="s">
+      <c r="B35" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="C35" s="18" t="s">
+      <c r="C35" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="D35" s="16" t="s">
+      <c r="D35" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="E35" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="F35" s="16"/>
-      <c r="G35" s="16"/>
-    </row>
-    <row r="36" spans="1:7" ht="25.35" hidden="1" x14ac:dyDescent="0.5">
-      <c r="A36" s="19">
+      <c r="E35" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="F35" s="14"/>
+      <c r="G35" s="14"/>
+    </row>
+    <row r="36" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A36" s="17">
         <v>28</v>
       </c>
-      <c r="B36" s="16" t="s">
+      <c r="B36" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="C36" s="18" t="s">
+      <c r="C36" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="D36" s="16" t="s">
+      <c r="D36" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="E36" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="F36" s="16"/>
-      <c r="G36" s="16"/>
-    </row>
-    <row r="37" spans="1:7" ht="25.35" hidden="1" x14ac:dyDescent="0.5">
-      <c r="A37" s="19">
+      <c r="E36" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="F36" s="14"/>
+      <c r="G36" s="14"/>
+    </row>
+    <row r="37" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A37" s="17">
         <v>29</v>
       </c>
-      <c r="B37" s="16" t="s">
+      <c r="B37" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="C37" s="18" t="s">
+      <c r="C37" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="D37" s="16" t="s">
+      <c r="D37" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="E37" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="F37" s="16"/>
-      <c r="G37" s="16"/>
-    </row>
-    <row r="38" spans="1:7" ht="25.35" hidden="1" x14ac:dyDescent="0.5">
-      <c r="A38" s="19">
+      <c r="E37" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="F37" s="14"/>
+      <c r="G37" s="14"/>
+    </row>
+    <row r="38" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A38" s="17">
         <v>30</v>
       </c>
-      <c r="B38" s="16" t="s">
+      <c r="B38" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="C38" s="18" t="s">
+      <c r="C38" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="D38" s="16" t="s">
+      <c r="D38" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="E38" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="F38" s="16"/>
-      <c r="G38" s="16"/>
-    </row>
-    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.5">
-      <c r="A39" s="19">
+      <c r="E38" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="F38" s="14"/>
+      <c r="G38" s="14"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="17">
         <v>31</v>
       </c>
-      <c r="B39" s="16" t="s">
+      <c r="B39" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="C39" s="18" t="s">
+      <c r="C39" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="D39" s="16" t="s">
+      <c r="D39" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="E39" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="F39" s="16"/>
-      <c r="G39" s="16"/>
-    </row>
-    <row r="40" spans="1:7" ht="25.35" hidden="1" x14ac:dyDescent="0.5">
-      <c r="A40" s="19">
+      <c r="E39" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="F39" s="14"/>
+      <c r="G39" s="14"/>
+    </row>
+    <row r="40" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A40" s="17">
         <v>32</v>
       </c>
-      <c r="B40" s="16" t="s">
+      <c r="B40" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="C40" s="18" t="s">
+      <c r="C40" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="D40" s="16" t="s">
+      <c r="D40" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="E40" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="F40" s="16"/>
-      <c r="G40" s="16"/>
-    </row>
-    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.5">
-      <c r="A41" s="19">
+      <c r="E40" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="F40" s="14"/>
+      <c r="G40" s="14"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="17">
         <v>33</v>
       </c>
-      <c r="B41" s="16" t="s">
+      <c r="B41" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="C41" s="18" t="s">
+      <c r="C41" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="D41" s="16" t="s">
+      <c r="D41" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="E41" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="F41" s="16"/>
-      <c r="G41" s="16"/>
-    </row>
-    <row r="42" spans="1:7" ht="25.35" hidden="1" x14ac:dyDescent="0.5">
-      <c r="A42" s="19">
+      <c r="E41" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="F41" s="14"/>
+      <c r="G41" s="14"/>
+    </row>
+    <row r="42" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A42" s="17">
         <v>34</v>
       </c>
-      <c r="B42" s="16" t="s">
+      <c r="B42" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="C42" s="18" t="s">
+      <c r="C42" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="D42" s="16" t="s">
+      <c r="D42" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="E42" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="F42" s="16"/>
-      <c r="G42" s="16"/>
-    </row>
-    <row r="43" spans="1:7" ht="25.35" hidden="1" x14ac:dyDescent="0.5">
-      <c r="A43" s="19">
+      <c r="E42" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="F42" s="14"/>
+      <c r="G42" s="14"/>
+    </row>
+    <row r="43" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A43" s="17">
         <v>35</v>
       </c>
-      <c r="B43" s="16" t="s">
+      <c r="B43" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="C43" s="18" t="s">
+      <c r="C43" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="D43" s="16" t="s">
+      <c r="D43" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="E43" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="F43" s="16"/>
-      <c r="G43" s="16"/>
-    </row>
-    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.5">
-      <c r="A44" s="19">
+      <c r="E43" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="F43" s="14"/>
+      <c r="G43" s="14"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="17">
         <v>36</v>
       </c>
-      <c r="B44" s="16" t="s">
+      <c r="B44" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="C44" s="18" t="s">
+      <c r="C44" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="D44" s="16" t="s">
+      <c r="D44" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="E44" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="F44" s="16"/>
-      <c r="G44" s="16"/>
-    </row>
-    <row r="45" spans="1:7" ht="25.35" hidden="1" x14ac:dyDescent="0.5">
-      <c r="A45" s="19">
+      <c r="E44" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="F44" s="14"/>
+      <c r="G44" s="14"/>
+    </row>
+    <row r="45" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A45" s="17">
         <v>37</v>
       </c>
-      <c r="B45" s="16" t="s">
+      <c r="B45" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="18" t="s">
+      <c r="C45" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="D45" s="16" t="s">
+      <c r="D45" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="E45" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="F45" s="16"/>
-      <c r="G45" s="16"/>
-    </row>
-    <row r="46" spans="1:7" ht="25.35" hidden="1" x14ac:dyDescent="0.5">
-      <c r="A46" s="19">
+      <c r="E45" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="F45" s="14"/>
+      <c r="G45" s="14"/>
+    </row>
+    <row r="46" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A46" s="17">
         <v>38</v>
       </c>
-      <c r="B46" s="16" t="s">
+      <c r="B46" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="C46" s="18" t="s">
+      <c r="C46" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="D46" s="16" t="s">
+      <c r="D46" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="E46" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="F46" s="16"/>
-      <c r="G46" s="16"/>
-    </row>
-    <row r="47" spans="1:7" ht="25.35" hidden="1" x14ac:dyDescent="0.5">
-      <c r="A47" s="19">
+      <c r="E46" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="F46" s="14"/>
+      <c r="G46" s="14"/>
+    </row>
+    <row r="47" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A47" s="17">
         <v>39</v>
       </c>
-      <c r="B47" s="16" t="s">
+      <c r="B47" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="C47" s="18" t="s">
+      <c r="C47" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="D47" s="16" t="s">
+      <c r="D47" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="E47" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="F47" s="16"/>
-      <c r="G47" s="16"/>
-    </row>
-    <row r="48" spans="1:7" ht="25.35" hidden="1" x14ac:dyDescent="0.5">
-      <c r="A48" s="19">
+      <c r="E47" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="F47" s="14"/>
+      <c r="G47" s="14"/>
+    </row>
+    <row r="48" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A48" s="17">
         <v>40</v>
       </c>
-      <c r="B48" s="16" t="s">
+      <c r="B48" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="C48" s="18" t="s">
+      <c r="C48" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="D48" s="16" t="s">
+      <c r="D48" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="E48" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="F48" s="16"/>
-      <c r="G48" s="16"/>
-    </row>
-    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.5">
-      <c r="A49" s="19">
+      <c r="E48" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="F48" s="14"/>
+      <c r="G48" s="14"/>
+    </row>
+    <row r="49" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A49" s="17">
         <v>41</v>
       </c>
-      <c r="B49" s="16" t="s">
+      <c r="B49" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="C49" s="18" t="s">
+      <c r="C49" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="D49" s="16" t="s">
+      <c r="D49" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="E49" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="F49" s="16"/>
-      <c r="G49" s="16"/>
-    </row>
-    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.5">
-      <c r="A50" s="19">
+      <c r="E49" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="F49" s="14"/>
+      <c r="G49" s="14"/>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" s="17">
         <v>42</v>
       </c>
-      <c r="B50" s="16" t="s">
+      <c r="B50" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="C50" s="18" t="s">
+      <c r="C50" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="D50" s="16" t="s">
+      <c r="D50" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="E50" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="F50" s="16"/>
-      <c r="G50" s="16"/>
-    </row>
-    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.5">
-      <c r="A51" s="19">
+      <c r="E50" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="F50" s="14"/>
+      <c r="G50" s="14"/>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" s="17">
         <v>43</v>
       </c>
-      <c r="B51" s="16" t="s">
+      <c r="B51" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="C51" s="18" t="s">
+      <c r="C51" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="D51" s="16" t="s">
+      <c r="D51" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="E51" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="F51" s="16"/>
-      <c r="G51" s="16"/>
-    </row>
-    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.5">
-      <c r="A52" s="19">
+      <c r="E51" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="F51" s="14"/>
+      <c r="G51" s="14"/>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" s="17">
         <v>44</v>
       </c>
-      <c r="B52" s="16" t="s">
+      <c r="B52" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="C52" s="18" t="s">
+      <c r="C52" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="D52" s="16" t="s">
+      <c r="D52" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="E52" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="F52" s="16"/>
-      <c r="G52" s="16"/>
+      <c r="E52" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="F52" s="14"/>
+      <c r="G52" s="14"/>
     </row>
   </sheetData>
-  <autoFilter ref="A8:G52" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="2. Database table and test data"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <mergeCells count="1">
     <mergeCell ref="A2:G2"/>
   </mergeCells>
@@ -2406,7 +2452,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9:E52">
-    <cfRule type="expression" dxfId="0" priority="2">
+    <cfRule type="expression" dxfId="3" priority="2">
       <formula>$E9="In progress"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2417,155 +2463,155 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02094B44-1383-4BD8-B536-1180EC67E71D}">
   <dimension ref="A1:D12"/>
-  <sheetFormatPr defaultColWidth="8.703125" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9" style="15" customWidth="1"/>
-    <col min="2" max="2" width="34" style="15" customWidth="1"/>
-    <col min="3" max="3" width="24" style="15" customWidth="1"/>
-    <col min="4" max="4" width="44" style="15" customWidth="1"/>
-    <col min="5" max="16384" width="8.703125" style="15"/>
+    <col min="1" max="1" width="9" style="13" customWidth="1"/>
+    <col min="2" max="2" width="34" style="13" customWidth="1"/>
+    <col min="3" max="3" width="24" style="13" customWidth="1"/>
+    <col min="4" max="4" width="44" style="13" customWidth="1"/>
+    <col min="5" max="16384" width="8.7109375" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="17.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="27" t="s">
+    <row r="1" spans="1:4" ht="18" x14ac:dyDescent="0.25">
+      <c r="A1" s="24" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A2" s="29" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="26" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A4" s="28" t="s">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="25" t="s">
         <v>190</v>
       </c>
-      <c r="B4" s="28" t="s">
+      <c r="B4" s="25" t="s">
         <v>189</v>
       </c>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="D4" s="28" t="s">
+      <c r="D4" s="25" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A5" s="19">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="17">
         <v>3</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="14" t="s">
         <v>187</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="D5" s="14" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A6" s="19">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="17">
         <v>4</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="14" t="s">
         <v>184</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="14" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A7" s="19">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="17">
         <v>5</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="14" t="s">
         <v>181</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="D7" s="14" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A8" s="19">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="17">
         <v>6</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="14" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A9" s="19">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="17">
         <v>7</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="14" t="s">
         <v>176</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C9" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="D9" s="14" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A10" s="19">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="17">
         <v>8</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="D10" s="14" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A11" s="19">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="17">
         <v>9</v>
       </c>
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="C11" s="16" t="s">
+      <c r="C11" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="D11" s="16" t="s">
+      <c r="D11" s="14" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A12" s="19">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="17">
         <v>10</v>
       </c>
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="C12" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="D12" s="16" t="s">
+      <c r="D12" s="14" t="s">
         <v>169</v>
       </c>
     </row>

--- a/project1/Z_Documentation/Project1_Tracker.xlsx
+++ b/project1/Z_Documentation/Project1_Tracker.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Games\Tools and Utilities\XAMPP\htdocs\database_javascript\project1\Z_Documentation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://waynestateprod-my.sharepoint.com/personal/gw3477_wayne_edu/Documents/DSE 6100/Project 1/database_javascript/project1/Z_Documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D74B42B2-57D5-4F7B-8640-2E05BD13A891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{D74B42B2-57D5-4F7B-8640-2E05BD13A891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D3647A0-7377-4BFC-ACF5-94C29C3D2A74}"/>
   <bookViews>
-    <workbookView xWindow="1185" yWindow="1815" windowWidth="21600" windowHeight="14130" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-93" yWindow="-93" windowWidth="25786" windowHeight="15466" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="File map" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,20 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Checklist!$A$8:$G$52</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'File map'!$A$4:$E$15</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -616,20 +629,33 @@
     <t>Not sure what this is talking about</t>
   </si>
   <si>
-    <t>Not sure what this means, we wouldn't use the registered date to find out users whom signed in today</t>
-  </si>
-  <si>
     <t>Not necessary, we just edit after login</t>
   </si>
   <si>
     <t>Necessary, we have to edit after login</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Not sure what this means, we wouldn't use the registered date to find out users whom signed in today
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>--- In the readme it says to return the students who 'registered' today, not signed in today</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -726,6 +752,13 @@
     </font>
     <font>
       <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -861,6 +894,12 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -870,18 +909,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{FEA456FB-2D08-45A4-B267-54834F765DE8}"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill>
@@ -896,20 +929,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFE2EFDA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF2CC"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1212,28 +1231,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="24.28515625" customWidth="1"/>
+    <col min="1" max="1" width="24.29296875" customWidth="1"/>
     <col min="2" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="80" customWidth="1"/>
     <col min="5" max="5" width="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="28" t="s">
+    <row r="1" spans="1:5" ht="17.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="29" t="s">
+      <c r="B1" s="30"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="A2" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -1250,7 +1269,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="25.35" x14ac:dyDescent="0.5">
       <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
@@ -1267,7 +1286,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" ht="25.35" x14ac:dyDescent="0.5">
       <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
@@ -1284,7 +1303,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" ht="25.35" x14ac:dyDescent="0.5">
       <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
@@ -1301,7 +1320,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" ht="38" x14ac:dyDescent="0.5">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
@@ -1318,7 +1337,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
@@ -1335,7 +1354,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="25.35" x14ac:dyDescent="0.5">
       <c r="A10" s="4" t="s">
         <v>24</v>
       </c>
@@ -1352,7 +1371,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="51" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" ht="50.7" x14ac:dyDescent="0.5">
       <c r="A11" s="6" t="s">
         <v>29</v>
       </c>
@@ -1369,7 +1388,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" ht="38" x14ac:dyDescent="0.5">
       <c r="A12" s="6" t="s">
         <v>29</v>
       </c>
@@ -1386,7 +1405,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" ht="25.35" x14ac:dyDescent="0.5">
       <c r="A13" s="6" t="s">
         <v>29</v>
       </c>
@@ -1403,7 +1422,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A14" s="6" t="s">
         <v>29</v>
       </c>
@@ -1420,7 +1439,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" ht="25.35" x14ac:dyDescent="0.5">
       <c r="A15" s="8" t="s">
         <v>43</v>
       </c>
@@ -1437,12 +1456,12 @@
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="15.35" x14ac:dyDescent="0.5">
       <c r="A17" s="10" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.5">
       <c r="B18" s="11" t="s">
         <v>49</v>
       </c>
@@ -1453,7 +1472,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.5">
       <c r="B19" s="12" t="s">
         <v>51</v>
       </c>
@@ -1464,7 +1483,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="38" x14ac:dyDescent="0.5">
       <c r="B20" s="12" t="s">
         <v>53</v>
       </c>
@@ -1475,7 +1494,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="51" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="50.7" x14ac:dyDescent="0.5">
       <c r="B21" s="12" t="s">
         <v>56</v>
       </c>
@@ -1499,7 +1518,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85571BBE-1456-4B5D-BA86-ED464C6FFE36}">
   <dimension ref="A1:G52"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.703125" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="5" style="13" customWidth="1"/>
     <col min="2" max="2" width="26" style="13" customWidth="1"/>
@@ -1507,31 +1526,31 @@
     <col min="4" max="4" width="70" style="13" customWidth="1"/>
     <col min="5" max="6" width="14" style="13" customWidth="1"/>
     <col min="7" max="7" width="28" style="13" customWidth="1"/>
-    <col min="8" max="16384" width="8.7109375" style="13"/>
+    <col min="8" max="16384" width="8.703125" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="17.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="24" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="27" t="s">
+    <row r="2" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A2" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A4" s="23" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.5">
       <c r="B5" s="20" t="s">
         <v>165</v>
       </c>
@@ -1547,7 +1566,7 @@
         <v>0.34090909090909088</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.5">
       <c r="B6" s="20" t="s">
         <v>151</v>
       </c>
@@ -1556,7 +1575,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.5">
       <c r="B7" s="20" t="s">
         <v>163</v>
       </c>
@@ -1565,7 +1584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A8" s="18" t="s">
         <v>162</v>
       </c>
@@ -1588,7 +1607,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="25.35" x14ac:dyDescent="0.5">
       <c r="A9" s="17">
         <v>1</v>
       </c>
@@ -1607,7 +1626,7 @@
       <c r="F9" s="14"/>
       <c r="G9" s="14"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A10" s="17">
         <v>2</v>
       </c>
@@ -1626,7 +1645,7 @@
       <c r="F10" s="14"/>
       <c r="G10" s="14"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A11" s="17">
         <v>3</v>
       </c>
@@ -1645,7 +1664,7 @@
       <c r="F11" s="14"/>
       <c r="G11" s="14"/>
     </row>
-    <row r="12" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="25.35" x14ac:dyDescent="0.5">
       <c r="A12" s="17">
         <v>4</v>
       </c>
@@ -1664,7 +1683,7 @@
       <c r="F12" s="14"/>
       <c r="G12" s="14"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A13" s="17">
         <v>5</v>
       </c>
@@ -1683,7 +1702,7 @@
       <c r="F13" s="14"/>
       <c r="G13" s="14"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A14" s="17">
         <v>6</v>
       </c>
@@ -1702,7 +1721,7 @@
       <c r="F14" s="14"/>
       <c r="G14" s="14"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A15" s="17">
         <v>7</v>
       </c>
@@ -1721,7 +1740,7 @@
       <c r="F15" s="14"/>
       <c r="G15" s="14"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A16" s="17">
         <v>8</v>
       </c>
@@ -1740,7 +1759,7 @@
       <c r="F16" s="14"/>
       <c r="G16" s="14"/>
     </row>
-    <row r="17" spans="1:7" ht="51" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="101.35" x14ac:dyDescent="0.5">
       <c r="A17" s="17">
         <v>9</v>
       </c>
@@ -1757,11 +1776,11 @@
         <v>59</v>
       </c>
       <c r="F17" s="14"/>
-      <c r="G17" s="31" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="G17" s="28" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="25.35" x14ac:dyDescent="0.5">
       <c r="A18" s="17">
         <v>10</v>
       </c>
@@ -1780,7 +1799,7 @@
       <c r="F18" s="14"/>
       <c r="G18" s="14"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A19" s="17">
         <v>11</v>
       </c>
@@ -1799,7 +1818,7 @@
       <c r="F19" s="14"/>
       <c r="G19" s="14"/>
     </row>
-    <row r="20" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="25.35" x14ac:dyDescent="0.5">
       <c r="A20" s="17">
         <v>12</v>
       </c>
@@ -1818,7 +1837,7 @@
       <c r="F20" s="14"/>
       <c r="G20" s="14"/>
     </row>
-    <row r="21" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="38" x14ac:dyDescent="0.5">
       <c r="A21" s="17">
         <v>13</v>
       </c>
@@ -1835,11 +1854,11 @@
         <v>151</v>
       </c>
       <c r="F21" s="14"/>
-      <c r="G21" s="30" t="s">
+      <c r="G21" s="27" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="25.35" x14ac:dyDescent="0.5">
       <c r="A22" s="17">
         <v>14</v>
       </c>
@@ -1856,11 +1875,11 @@
         <v>151</v>
       </c>
       <c r="F22" s="14"/>
-      <c r="G22" s="30" t="s">
+      <c r="G22" s="27" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A23" s="17">
         <v>15</v>
       </c>
@@ -1877,11 +1896,11 @@
         <v>151</v>
       </c>
       <c r="F23" s="14"/>
-      <c r="G23" s="30" t="s">
+      <c r="G23" s="27" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A24" s="17">
         <v>16</v>
       </c>
@@ -1900,7 +1919,7 @@
       <c r="F24" s="14"/>
       <c r="G24" s="14"/>
     </row>
-    <row r="25" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="25.35" x14ac:dyDescent="0.5">
       <c r="A25" s="17">
         <v>17</v>
       </c>
@@ -1919,7 +1938,7 @@
       <c r="F25" s="14"/>
       <c r="G25" s="14"/>
     </row>
-    <row r="26" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="38" x14ac:dyDescent="0.5">
       <c r="A26" s="17">
         <v>18</v>
       </c>
@@ -1938,7 +1957,7 @@
       <c r="F26" s="14"/>
       <c r="G26" s="14"/>
     </row>
-    <row r="27" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="25.35" x14ac:dyDescent="0.5">
       <c r="A27" s="17">
         <v>19</v>
       </c>
@@ -1957,7 +1976,7 @@
       <c r="F27" s="14"/>
       <c r="G27" s="14"/>
     </row>
-    <row r="28" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="25.35" x14ac:dyDescent="0.5">
       <c r="A28" s="17">
         <v>20</v>
       </c>
@@ -1975,10 +1994,10 @@
       </c>
       <c r="F28" s="14"/>
       <c r="G28" s="14" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="25.35" x14ac:dyDescent="0.5">
       <c r="A29" s="17">
         <v>21</v>
       </c>
@@ -1996,10 +2015,10 @@
       </c>
       <c r="F29" s="14"/>
       <c r="G29" s="14" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="25.35" x14ac:dyDescent="0.5">
       <c r="A30" s="17">
         <v>22</v>
       </c>
@@ -2017,10 +2036,10 @@
       </c>
       <c r="F30" s="14"/>
       <c r="G30" s="14" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="25.35" x14ac:dyDescent="0.5">
       <c r="A31" s="17">
         <v>23</v>
       </c>
@@ -2038,10 +2057,10 @@
       </c>
       <c r="F31" s="14"/>
       <c r="G31" s="14" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="25.35" x14ac:dyDescent="0.5">
       <c r="A32" s="17">
         <v>24</v>
       </c>
@@ -2059,10 +2078,10 @@
       </c>
       <c r="F32" s="14"/>
       <c r="G32" s="14" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="25.35" x14ac:dyDescent="0.5">
       <c r="A33" s="17">
         <v>25</v>
       </c>
@@ -2081,7 +2100,7 @@
       <c r="F33" s="14"/>
       <c r="G33" s="14"/>
     </row>
-    <row r="34" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" ht="25.35" x14ac:dyDescent="0.5">
       <c r="A34" s="17">
         <v>26</v>
       </c>
@@ -2100,7 +2119,7 @@
       <c r="F34" s="14"/>
       <c r="G34" s="14"/>
     </row>
-    <row r="35" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" ht="25.35" x14ac:dyDescent="0.5">
       <c r="A35" s="17">
         <v>27</v>
       </c>
@@ -2119,7 +2138,7 @@
       <c r="F35" s="14"/>
       <c r="G35" s="14"/>
     </row>
-    <row r="36" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" ht="25.35" x14ac:dyDescent="0.5">
       <c r="A36" s="17">
         <v>28</v>
       </c>
@@ -2138,7 +2157,7 @@
       <c r="F36" s="14"/>
       <c r="G36" s="14"/>
     </row>
-    <row r="37" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" ht="25.35" x14ac:dyDescent="0.5">
       <c r="A37" s="17">
         <v>29</v>
       </c>
@@ -2157,7 +2176,7 @@
       <c r="F37" s="14"/>
       <c r="G37" s="14"/>
     </row>
-    <row r="38" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" ht="25.35" x14ac:dyDescent="0.5">
       <c r="A38" s="17">
         <v>30</v>
       </c>
@@ -2176,7 +2195,7 @@
       <c r="F38" s="14"/>
       <c r="G38" s="14"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A39" s="17">
         <v>31</v>
       </c>
@@ -2195,7 +2214,7 @@
       <c r="F39" s="14"/>
       <c r="G39" s="14"/>
     </row>
-    <row r="40" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" ht="25.35" x14ac:dyDescent="0.5">
       <c r="A40" s="17">
         <v>32</v>
       </c>
@@ -2214,7 +2233,7 @@
       <c r="F40" s="14"/>
       <c r="G40" s="14"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A41" s="17">
         <v>33</v>
       </c>
@@ -2233,7 +2252,7 @@
       <c r="F41" s="14"/>
       <c r="G41" s="14"/>
     </row>
-    <row r="42" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" ht="25.35" x14ac:dyDescent="0.5">
       <c r="A42" s="17">
         <v>34</v>
       </c>
@@ -2252,7 +2271,7 @@
       <c r="F42" s="14"/>
       <c r="G42" s="14"/>
     </row>
-    <row r="43" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" ht="25.35" x14ac:dyDescent="0.5">
       <c r="A43" s="17">
         <v>35</v>
       </c>
@@ -2271,7 +2290,7 @@
       <c r="F43" s="14"/>
       <c r="G43" s="14"/>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A44" s="17">
         <v>36</v>
       </c>
@@ -2290,7 +2309,7 @@
       <c r="F44" s="14"/>
       <c r="G44" s="14"/>
     </row>
-    <row r="45" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" ht="25.35" x14ac:dyDescent="0.5">
       <c r="A45" s="17">
         <v>37</v>
       </c>
@@ -2309,7 +2328,7 @@
       <c r="F45" s="14"/>
       <c r="G45" s="14"/>
     </row>
-    <row r="46" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" ht="25.35" x14ac:dyDescent="0.5">
       <c r="A46" s="17">
         <v>38</v>
       </c>
@@ -2328,7 +2347,7 @@
       <c r="F46" s="14"/>
       <c r="G46" s="14"/>
     </row>
-    <row r="47" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" ht="25.35" x14ac:dyDescent="0.5">
       <c r="A47" s="17">
         <v>39</v>
       </c>
@@ -2347,7 +2366,7 @@
       <c r="F47" s="14"/>
       <c r="G47" s="14"/>
     </row>
-    <row r="48" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" ht="25.35" x14ac:dyDescent="0.5">
       <c r="A48" s="17">
         <v>40</v>
       </c>
@@ -2366,7 +2385,7 @@
       <c r="F48" s="14"/>
       <c r="G48" s="14"/>
     </row>
-    <row r="49" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A49" s="17">
         <v>41</v>
       </c>
@@ -2385,7 +2404,7 @@
       <c r="F49" s="14"/>
       <c r="G49" s="14"/>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A50" s="17">
         <v>42</v>
       </c>
@@ -2404,7 +2423,7 @@
       <c r="F50" s="14"/>
       <c r="G50" s="14"/>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A51" s="17">
         <v>43</v>
       </c>
@@ -2423,7 +2442,7 @@
       <c r="F51" s="14"/>
       <c r="G51" s="14"/>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A52" s="17">
         <v>44</v>
       </c>
@@ -2452,7 +2471,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9:E52">
-    <cfRule type="expression" dxfId="3" priority="2">
+    <cfRule type="expression" dxfId="0" priority="2">
       <formula>$E9="In progress"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2470,26 +2489,26 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02094B44-1383-4BD8-B536-1180EC67E71D}">
   <dimension ref="A1:D12"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.703125" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="9" style="13" customWidth="1"/>
     <col min="2" max="2" width="34" style="13" customWidth="1"/>
     <col min="3" max="3" width="24" style="13" customWidth="1"/>
     <col min="4" max="4" width="44" style="13" customWidth="1"/>
-    <col min="5" max="16384" width="8.7109375" style="13"/>
+    <col min="5" max="16384" width="8.703125" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="17.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="24" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A2" s="26" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A4" s="25" t="s">
         <v>190</v>
       </c>
@@ -2503,7 +2522,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A5" s="17">
         <v>3</v>
       </c>
@@ -2517,7 +2536,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A6" s="17">
         <v>4</v>
       </c>
@@ -2531,7 +2550,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A7" s="17">
         <v>5</v>
       </c>
@@ -2545,7 +2564,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A8" s="17">
         <v>6</v>
       </c>
@@ -2559,7 +2578,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A9" s="17">
         <v>7</v>
       </c>
@@ -2573,7 +2592,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A10" s="17">
         <v>8</v>
       </c>
@@ -2587,7 +2606,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A11" s="17">
         <v>9</v>
       </c>
@@ -2601,7 +2620,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A12" s="17">
         <v>10</v>
       </c>

--- a/project1/Z_Documentation/Project1_Tracker.xlsx
+++ b/project1/Z_Documentation/Project1_Tracker.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://waynestateprod-my.sharepoint.com/personal/gw3477_wayne_edu/Documents/DSE 6100/Project 1/database_javascript/project1/Z_Documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{D74B42B2-57D5-4F7B-8640-2E05BD13A891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D3647A0-7377-4BFC-ACF5-94C29C3D2A74}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="13_ncr:1_{D74B42B2-57D5-4F7B-8640-2E05BD13A891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC0999CC-7F2C-437E-BF7C-C51E2E04ED2F}"/>
   <bookViews>
-    <workbookView xWindow="-93" yWindow="-93" windowWidth="25786" windowHeight="15466" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-107" yWindow="-107" windowWidth="25814" windowHeight="15494" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="File map" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Search Panel" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Checklist!$A$8:$G$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Checklist!$A$8:$G$48</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'File map'!$A$4:$E$15</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="190">
   <si>
     <t>DSE 6100 Project 1: main files</t>
   </si>
@@ -356,36 +356,9 @@
     <t>On the dashboard, using the existing PATCH /update/Users route (needs the profile-update fix in section 1).</t>
   </si>
   <si>
-    <t>Optional: edit-profile form</t>
-  </si>
-  <si>
     <t>3. Profile fields</t>
   </si>
   <si>
-    <t>dbService.js insertNewUser: accept the fields and add them to the INSERT.</t>
-  </si>
-  <si>
-    <t>Insert query</t>
-  </si>
-  <si>
-    <t>app.js line 146: read the new fields from the request.</t>
-  </si>
-  <si>
-    <t>Register route</t>
-  </si>
-  <si>
-    <t>index.js line 60: send the four new fields along with the username and password.</t>
-  </si>
-  <si>
-    <t>Register request</t>
-  </si>
-  <si>
-    <t>index.html: add first name, last name, salary and age inputs.</t>
-  </si>
-  <si>
-    <t>Register form</t>
-  </si>
-  <si>
     <t>Test users inserted with SQL can't sign in, because their passwords aren't hashed.</t>
   </si>
   <si>
@@ -627,12 +600,6 @@
   </si>
   <si>
     <t>Not sure what this is talking about</t>
-  </si>
-  <si>
-    <t>Not necessary, we just edit after login</t>
-  </si>
-  <si>
-    <t>Necessary, we have to edit after login</t>
   </si>
   <si>
     <r>
@@ -650,12 +617,18 @@
       <t>--- In the readme it says to return the students who 'registered' today, not signed in today</t>
     </r>
   </si>
+  <si>
+    <t>edit-profile form</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -758,6 +731,12 @@
     <font>
       <b/>
       <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -830,7 +809,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -900,6 +879,9 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -943,6 +925,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1240,17 +1226,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="17.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30"/>
+      <c r="B1" s="31"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A4" s="1" t="s">
@@ -1517,12 +1503,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85571BBE-1456-4B5D-BA86-ED464C6FFE36}">
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr defaultColWidth="8.703125" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="5" style="13" customWidth="1"/>
     <col min="2" max="2" width="26" style="13" customWidth="1"/>
-    <col min="3" max="3" width="30" style="13" customWidth="1"/>
+    <col min="3" max="3" width="26.64453125" style="13" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="70" style="13" customWidth="1"/>
     <col min="5" max="6" width="14" style="13" customWidth="1"/>
     <col min="7" max="7" width="28" style="13" customWidth="1"/>
@@ -1531,80 +1517,80 @@
   <sheetData>
     <row r="1" spans="1:7" ht="17.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="24" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="29" t="s">
-        <v>167</v>
-      </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
+      <c r="A2" s="30" t="s">
+        <v>158</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A4" s="23" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.5">
       <c r="B5" s="20" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="C5" s="19">
-        <f>COUNTA(C9:C52)</f>
-        <v>44</v>
+        <f>COUNTA(C9:C48)</f>
+        <v>40</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="E5" s="21">
         <f>IFERROR(C6/C5,0)</f>
-        <v>0.34090909090909088</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.5">
       <c r="B6" s="20" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="C6" s="19">
-        <f>COUNTIF(E9:E52,"Done")</f>
-        <v>15</v>
+        <f>COUNTIF(E9:E48,"Done")</f>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.5">
       <c r="B7" s="20" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="C7" s="19">
-        <f>COUNTIF(E9:E52,"In progress")</f>
-        <v>0</v>
+        <f>COUNTIF(E9:E48,"In progress")</f>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A8" s="18" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="E8" s="18" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F8" s="18" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="G8" s="18" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="25.35" x14ac:dyDescent="0.5">
@@ -1612,16 +1598,16 @@
         <v>1</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="F9" s="14"/>
       <c r="G9" s="14"/>
@@ -1631,16 +1617,16 @@
         <v>2</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="F10" s="14"/>
       <c r="G10" s="14"/>
@@ -1650,16 +1636,16 @@
         <v>3</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="F11" s="14"/>
       <c r="G11" s="14"/>
@@ -1669,16 +1655,16 @@
         <v>4</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="F12" s="14"/>
       <c r="G12" s="14"/>
@@ -1688,16 +1674,16 @@
         <v>5</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="F13" s="14"/>
       <c r="G13" s="14"/>
@@ -1707,16 +1693,16 @@
         <v>6</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="F14" s="14"/>
       <c r="G14" s="14"/>
@@ -1726,16 +1712,16 @@
         <v>7</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="C15" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="E15" s="15" t="s">
         <v>142</v>
-      </c>
-      <c r="D15" s="14" t="s">
-        <v>141</v>
-      </c>
-      <c r="E15" s="15" t="s">
-        <v>151</v>
       </c>
       <c r="F15" s="14"/>
       <c r="G15" s="14"/>
@@ -1745,16 +1731,16 @@
         <v>8</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="F16" s="14"/>
       <c r="G16" s="14"/>
@@ -1764,20 +1750,20 @@
         <v>9</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>59</v>
+        <v>142</v>
       </c>
       <c r="F17" s="14"/>
       <c r="G17" s="28" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="25.35" x14ac:dyDescent="0.5">
@@ -1785,16 +1771,16 @@
         <v>10</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="F18" s="14"/>
       <c r="G18" s="14"/>
@@ -1804,16 +1790,16 @@
         <v>11</v>
       </c>
       <c r="B19" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="D19" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="C19" s="16" t="s">
-        <v>134</v>
-      </c>
-      <c r="D19" s="14" t="s">
-        <v>133</v>
-      </c>
       <c r="E19" s="15" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="F19" s="14"/>
       <c r="G19" s="14"/>
@@ -1823,16 +1809,16 @@
         <v>12</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="F20" s="14"/>
       <c r="G20" s="14"/>
@@ -1842,20 +1828,20 @@
         <v>13</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="F21" s="14"/>
       <c r="G21" s="27" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="25.35" x14ac:dyDescent="0.5">
@@ -1863,20 +1849,20 @@
         <v>14</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="F22" s="14"/>
       <c r="G22" s="27" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.5">
@@ -1884,20 +1870,20 @@
         <v>15</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="F23" s="14"/>
       <c r="G23" s="27" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.5">
@@ -1905,13 +1891,13 @@
         <v>16</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="E24" s="15" t="s">
         <v>59</v>
@@ -1924,16 +1910,16 @@
         <v>17</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>59</v>
+        <v>154</v>
       </c>
       <c r="F25" s="14"/>
       <c r="G25" s="14"/>
@@ -1943,16 +1929,16 @@
         <v>18</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>59</v>
+        <v>154</v>
       </c>
       <c r="F26" s="14"/>
       <c r="G26" s="14"/>
@@ -1962,137 +1948,129 @@
         <v>19</v>
       </c>
       <c r="B27" s="14" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>59</v>
+        <v>154</v>
       </c>
       <c r="F27" s="14"/>
       <c r="G27" s="14"/>
     </row>
     <row r="28" spans="1:7" ht="25.35" x14ac:dyDescent="0.5">
       <c r="A28" s="17">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B28" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="C28" s="16" t="s">
-        <v>114</v>
+        <v>105</v>
+      </c>
+      <c r="C28" s="29" t="s">
+        <v>188</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="E28" s="15" t="s">
         <v>59</v>
       </c>
       <c r="F28" s="14"/>
-      <c r="G28" s="14" t="s">
-        <v>196</v>
-      </c>
+      <c r="G28" s="14"/>
     </row>
     <row r="29" spans="1:7" ht="25.35" x14ac:dyDescent="0.5">
       <c r="A29" s="17">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B29" s="14" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>112</v>
-      </c>
-      <c r="D29" s="14" t="s">
-        <v>111</v>
+        <v>103</v>
+      </c>
+      <c r="D29" s="28" t="s">
+        <v>102</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>59</v>
+        <v>154</v>
       </c>
       <c r="F29" s="14"/>
-      <c r="G29" s="14" t="s">
-        <v>196</v>
+      <c r="G29" s="28" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="25.35" x14ac:dyDescent="0.5">
       <c r="A30" s="17">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B30" s="14" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="E30" s="15" t="s">
-        <v>59</v>
+        <v>142</v>
       </c>
       <c r="F30" s="14"/>
-      <c r="G30" s="14" t="s">
-        <v>196</v>
-      </c>
+      <c r="G30" s="14"/>
     </row>
     <row r="31" spans="1:7" ht="25.35" x14ac:dyDescent="0.5">
       <c r="A31" s="17">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B31" s="14" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="E31" s="15" t="s">
-        <v>59</v>
+        <v>154</v>
       </c>
       <c r="F31" s="14"/>
-      <c r="G31" s="14" t="s">
-        <v>196</v>
-      </c>
+      <c r="G31" s="14"/>
     </row>
     <row r="32" spans="1:7" ht="25.35" x14ac:dyDescent="0.5">
       <c r="A32" s="17">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B32" s="14" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="E32" s="15" t="s">
-        <v>59</v>
+        <v>154</v>
       </c>
       <c r="F32" s="14"/>
-      <c r="G32" s="14" t="s">
-        <v>197</v>
-      </c>
+      <c r="G32" s="14"/>
     </row>
     <row r="33" spans="1:7" ht="25.35" x14ac:dyDescent="0.5">
       <c r="A33" s="17">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B33" s="14" t="s">
         <v>95</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="D33" s="14" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="E33" s="15" t="s">
         <v>59</v>
@@ -2102,168 +2080,168 @@
     </row>
     <row r="34" spans="1:7" ht="25.35" x14ac:dyDescent="0.5">
       <c r="A34" s="17">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B34" s="14" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="E34" s="15" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="F34" s="14"/>
       <c r="G34" s="14"/>
     </row>
-    <row r="35" spans="1:7" ht="25.35" x14ac:dyDescent="0.5">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A35" s="17">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B35" s="14" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="C35" s="16" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="D35" s="14" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="E35" s="15" t="s">
-        <v>59</v>
+        <v>154</v>
       </c>
       <c r="F35" s="14"/>
       <c r="G35" s="14"/>
     </row>
     <row r="36" spans="1:7" ht="25.35" x14ac:dyDescent="0.5">
       <c r="A36" s="17">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B36" s="14" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="D36" s="14" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="E36" s="15" t="s">
-        <v>59</v>
+        <v>154</v>
       </c>
       <c r="F36" s="14"/>
       <c r="G36" s="14"/>
     </row>
-    <row r="37" spans="1:7" ht="25.35" x14ac:dyDescent="0.5">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A37" s="17">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B37" s="14" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="C37" s="16" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D37" s="14" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="E37" s="15" t="s">
-        <v>59</v>
+        <v>154</v>
       </c>
       <c r="F37" s="14"/>
       <c r="G37" s="14"/>
     </row>
     <row r="38" spans="1:7" ht="25.35" x14ac:dyDescent="0.5">
       <c r="A38" s="17">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B38" s="14" t="s">
         <v>80</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="D38" s="14" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="E38" s="15" t="s">
-        <v>59</v>
+        <v>154</v>
       </c>
       <c r="F38" s="14"/>
       <c r="G38" s="14"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="39" spans="1:7" ht="25.35" x14ac:dyDescent="0.5">
       <c r="A39" s="17">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B39" s="14" t="s">
         <v>80</v>
       </c>
       <c r="C39" s="16" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="D39" s="14" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="E39" s="15" t="s">
-        <v>59</v>
+        <v>154</v>
       </c>
       <c r="F39" s="14"/>
       <c r="G39" s="14"/>
     </row>
-    <row r="40" spans="1:7" ht="25.35" x14ac:dyDescent="0.5">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A40" s="17">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B40" s="14" t="s">
         <v>80</v>
       </c>
       <c r="C40" s="16" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="D40" s="14" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="E40" s="15" t="s">
-        <v>59</v>
+        <v>154</v>
       </c>
       <c r="F40" s="14"/>
       <c r="G40" s="14"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="41" spans="1:7" ht="25.35" x14ac:dyDescent="0.5">
       <c r="A41" s="17">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B41" s="14" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C41" s="16" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="D41" s="14" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="E41" s="15" t="s">
-        <v>59</v>
+        <v>154</v>
       </c>
       <c r="F41" s="14"/>
       <c r="G41" s="14"/>
     </row>
     <row r="42" spans="1:7" ht="25.35" x14ac:dyDescent="0.5">
       <c r="A42" s="17">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B42" s="14" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C42" s="16" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="D42" s="14" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="E42" s="15" t="s">
         <v>59</v>
@@ -2273,16 +2251,16 @@
     </row>
     <row r="43" spans="1:7" ht="25.35" x14ac:dyDescent="0.5">
       <c r="A43" s="17">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B43" s="14" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C43" s="16" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="D43" s="14" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="E43" s="15" t="s">
         <v>59</v>
@@ -2290,18 +2268,18 @@
       <c r="F43" s="14"/>
       <c r="G43" s="14"/>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="44" spans="1:7" ht="25.35" x14ac:dyDescent="0.5">
       <c r="A44" s="17">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B44" s="14" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C44" s="16" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="D44" s="14" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="E44" s="15" t="s">
         <v>59</v>
@@ -2309,18 +2287,18 @@
       <c r="F44" s="14"/>
       <c r="G44" s="14"/>
     </row>
-    <row r="45" spans="1:7" ht="25.35" x14ac:dyDescent="0.5">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A45" s="17">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B45" s="14" t="s">
         <v>69</v>
       </c>
       <c r="C45" s="16" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D45" s="14" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="E45" s="15" t="s">
         <v>59</v>
@@ -2328,18 +2306,18 @@
       <c r="F45" s="14"/>
       <c r="G45" s="14"/>
     </row>
-    <row r="46" spans="1:7" ht="25.35" x14ac:dyDescent="0.5">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A46" s="17">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B46" s="14" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="C46" s="16" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="D46" s="14" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="E46" s="15" t="s">
         <v>59</v>
@@ -2347,18 +2325,18 @@
       <c r="F46" s="14"/>
       <c r="G46" s="14"/>
     </row>
-    <row r="47" spans="1:7" ht="25.35" x14ac:dyDescent="0.5">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A47" s="17">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B47" s="14" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="C47" s="16" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="D47" s="14" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="E47" s="15" t="s">
         <v>59</v>
@@ -2366,117 +2344,41 @@
       <c r="F47" s="14"/>
       <c r="G47" s="14"/>
     </row>
-    <row r="48" spans="1:7" ht="25.35" x14ac:dyDescent="0.5">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A48" s="17">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B48" s="14" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="C48" s="16" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="D48" s="14" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E48" s="15" t="s">
         <v>59</v>
       </c>
       <c r="F48" s="14"/>
       <c r="G48" s="14"/>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.5">
-      <c r="A49" s="17">
-        <v>41</v>
-      </c>
-      <c r="B49" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="C49" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="D49" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="E49" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="F49" s="14"/>
-      <c r="G49" s="14"/>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.5">
-      <c r="A50" s="17">
-        <v>42</v>
-      </c>
-      <c r="B50" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="C50" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="D50" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="E50" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="F50" s="14"/>
-      <c r="G50" s="14"/>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.5">
-      <c r="A51" s="17">
-        <v>43</v>
-      </c>
-      <c r="B51" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="C51" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="D51" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="E51" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14"/>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.5">
-      <c r="A52" s="17">
-        <v>44</v>
-      </c>
-      <c r="B52" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="C52" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="D52" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="E52" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="F52" s="14"/>
-      <c r="G52" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:G2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A9:G52">
+  <conditionalFormatting sqref="A9:G48">
     <cfRule type="expression" dxfId="1" priority="1">
       <formula>$E9="Done"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E9:E52">
+  <conditionalFormatting sqref="E9:E48">
     <cfRule type="expression" dxfId="0" priority="2">
       <formula>$E9="In progress"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="E9:E52" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" sqref="E9:E48" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Not started,In progress,Done"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -2500,26 +2402,26 @@
   <sheetData>
     <row r="1" spans="1:4" ht="17.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="24" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A2" s="26" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A4" s="25" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="B4" s="25" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="C4" s="25" t="s">
         <v>88</v>
       </c>
       <c r="D4" s="25" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.5">
@@ -2527,13 +2429,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.5">
@@ -2541,13 +2443,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.5">
@@ -2555,13 +2457,13 @@
         <v>5</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.5">
@@ -2569,13 +2471,13 @@
         <v>6</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.5">
@@ -2583,13 +2485,13 @@
         <v>7</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.5">
@@ -2597,13 +2499,13 @@
         <v>8</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.5">
@@ -2611,13 +2513,13 @@
         <v>9</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.5">
@@ -2625,13 +2527,13 @@
         <v>10</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
     </row>
   </sheetData>
